--- a/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
+++ b/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
+++ b/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
+++ b/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
+++ b/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
+++ b/StructureDefinition-SEEHDSRivCVTypeCrmRequeststatus2.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
